--- a/Mass_update_KAIKU/mass_update_kaiku_sts_fix.xlsx
+++ b/Mass_update_KAIKU/mass_update_kaiku_sts_fix.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a0R6g00000H0Qv5</t>
+          <t>a0R6g00000H0QvK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
+          <t>60801000001SK</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
@@ -550,7 +550,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a0R6g00000H2Fcv</t>
+          <t>a0R6g00000H2Fcx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,15 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>45231</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>10434_KAI01_2</t>
@@ -576,7 +578,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1570000020S</t>
+          <t>60000000100SK</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -598,7 +600,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a0R6g00000H0QvB</t>
+          <t>a0R6g00000H0Qv5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,12 +626,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>60502000000SK</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>45231</v>
+      </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -639,12 +643,14 @@
       <c r="K4" s="2" t="n">
         <v>37691</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" s="2" t="n">
+        <v>45350</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a0R6g00000H0QvK</t>
+          <t>a0R6g00000H2Fcv</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,12 +676,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>45231</v>
-      </c>
+          <t>1570000020S</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>1</v>
       </c>
@@ -694,7 +698,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>a0R6g00000H2Fcx</t>
+          <t>a0R6g00000H0QvA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -704,17 +708,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>45231</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>10434_KAI01_2</t>
@@ -722,7 +724,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>60000000100SK</t>
+          <t>#KAIKU</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -737,14 +739,12 @@
       <c r="K6" s="2" t="n">
         <v>37691</v>
       </c>
-      <c r="L6" s="2" t="n">
-        <v>45350</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>a0R6g00000H0QvA</t>
+          <t>a0R6g00000H0QvB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
+          <t>#KAIKU_SW</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>a0R3g000009enf4</t>
+          <t>a0R3g000009enf1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>15700000007</t>
+          <t>15700000001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -838,12 +838,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>a0R3g000009enf7</t>
+          <t>a0R3g000009enf4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>15700000012</t>
+          <t>15700000007</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -886,25 +886,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>a0R3g000009enf1</t>
+          <t>a0R3g000009enf7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Installed</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Shipped</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>44673</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>10451_KAI01_2</t>
@@ -912,7 +914,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15700000001</t>
+          <t>15700000012</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -980,7 +982,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>a0R6g00000H2nFe</t>
+          <t>a0R6g00000H2nFo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1006,7 +1008,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
+          <t>60801000001SK</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
@@ -1030,7 +1032,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg57l</t>
+          <t>a0R6g00000Hg57n</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1058,7 +1060,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15700000016</t>
+          <t>60000000100SK</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1080,7 +1082,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg57n</t>
+          <t>a0R6g00000H2nFe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1090,28 +1092,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10491_KAI01_2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>60502000000SK</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
         <v>45378</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>10491_KAI01_2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>60000000100SK</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>1</v>
       </c>
@@ -1130,7 +1132,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>a0R6g00000H2nFo</t>
+          <t>a0R6g00000H2nFj</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1156,12 +1158,10 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>45378</v>
-      </c>
+          <t>#KAIKU</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>1</v>
       </c>
@@ -1173,9 +1173,7 @@
       <c r="K15" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L15" s="2" t="n">
-        <v>45581</v>
-      </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1226,7 +1224,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg57k</t>
+          <t>a0R6g00000Hg57l</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1254,7 +1252,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15700000014</t>
+          <t>15700000016</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1276,7 +1274,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>a0R6g00000Hg57m</t>
+          <t>a0R6g00000Hg57k</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1304,7 +1302,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15700000028</t>
+          <t>15700000014</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1326,7 +1324,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>a0R6g00000H2nFj</t>
+          <t>a0R6g00000Hg57m</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1336,15 +1334,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>45378</v>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>10491_KAI01_2</t>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
+          <t>15700000028</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1367,12 +1367,14 @@
       <c r="K19" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" s="2" t="n">
+        <v>45581</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a0RKf00000HqRoA</t>
+          <t>a0RKf00000HqRnL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1382,28 +1384,28 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Not in Clinical Use</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>11392_SMA001_2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1570000020S</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
         <v>45820</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>11392_SMA001_2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>#KAIKU</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>1</v>
       </c>
@@ -1415,12 +1417,14 @@
       <c r="K20" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" s="2" t="n">
+        <v>45820</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>a0RKf00000HqRnL</t>
+          <t>a0RKf00000HqRoA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1430,15 +1434,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Not in Clinical Use</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>45820</v>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>11392_SMA001_2</t>
@@ -1446,12 +1452,10 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1570000020S</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>45820</v>
-      </c>
+          <t>#KAIKU</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>1</v>
       </c>
@@ -1463,14 +1467,12 @@
       <c r="K21" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L21" s="2" t="n">
-        <v>45820</v>
-      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>a0RKf00000HqRnM</t>
+          <t>a0RKf00000HqRoB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1496,12 +1498,10 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15700000028</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>45820</v>
-      </c>
+          <t>#KAIKU_SW</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
         <v>1</v>
       </c>
@@ -1513,14 +1513,12 @@
       <c r="K22" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L22" s="2" t="n">
-        <v>45820</v>
-      </c>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>a0RKf00000HqRoB</t>
+          <t>a0RKf00000HqRnM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1546,10 +1544,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>15700000028</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>45820</v>
+      </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
@@ -1561,7 +1561,9 @@
       <c r="K23" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" s="2" t="n">
+        <v>45820</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1614,7 +1616,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>a0R6g00000F09sa</t>
+          <t>a0R6g00000EUln5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1640,7 +1642,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
+          <t>15700000027</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1662,7 +1664,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>a0R6g00000EUln0</t>
+          <t>a0R6g00000HgdMa</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1672,15 +1674,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>45016</v>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>11596_PLZ01_2</t>
@@ -1688,7 +1692,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15700000014</t>
+          <t>15700000027</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1704,13 +1708,13 @@
         <v>38286</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>45016</v>
+        <v>45679</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>a0R6g00000EUln2</t>
+          <t>a0R6g00000F09sa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1736,7 +1740,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>15700000016</t>
+          <t>#KAIKU_SW</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1758,7 +1762,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>a0R6g00000EUln5</t>
+          <t>a0R6g00000EUln2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1784,7 +1788,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15700000027</t>
+          <t>15700000016</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1806,7 +1810,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>a0R6g00000HgdMa</t>
+          <t>a0R6g00000EUln0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1816,12 +1820,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1832,7 +1836,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15700000027</t>
+          <t>15700000014</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1848,13 +1852,13 @@
         <v>38286</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>45679</v>
+        <v>45016</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>a0R3g000009enf2</t>
+          <t>a0R3g0000080gIw</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1864,12 +1868,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1880,13 +1884,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15700000001</t>
+          <t>#KAIKU</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>RNCA</t>
@@ -1895,14 +1897,12 @@
       <c r="K30" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L30" s="2" t="n">
-        <v>44673</v>
-      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>a0R3g000009enf8</t>
+          <t>a0R3g000009enf2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1920,7 +1920,9 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" s="3" t="n">
+        <v>44294</v>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>12213_KAI01_2</t>
@@ -1928,12 +1930,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>15700000012</t>
+          <t>15700000001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1950,7 +1952,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>a0RKf00000JPBkk</t>
+          <t>a0R3g000008LwK0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1960,12 +1962,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1976,7 +1978,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>15700000027</t>
+          <t>15700000001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1991,14 +1993,12 @@
       <c r="K32" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L32" s="2" t="n">
-        <v>45888</v>
-      </c>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>a0RKf00000JPBkj</t>
+          <t>a0R3g0000080gJb</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2024,13 +2024,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>15700000016</t>
+          <t>1570000021S</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="n">
-        <v>1</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>RNCA</t>
@@ -2039,14 +2037,12 @@
       <c r="K33" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L33" s="2" t="n">
-        <v>45888</v>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>a0R3g0000080gJb</t>
+          <t>a0R3g000009enf8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2056,15 +2052,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>44294</v>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>12213_KAI01_2</t>
@@ -2072,11 +2070,13 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1570000021S</t>
+          <t>15700000012</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>RNCA</t>
@@ -2085,12 +2085,14 @@
       <c r="K34" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" s="2" t="n">
+        <v>44673</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>a0R3g0000080gJq</t>
+          <t>a0RKf00000JPBkk</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2100,15 +2102,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>44294</v>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>12213_KAI01_2</t>
@@ -2116,11 +2120,13 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15700000016</t>
+          <t>15700000027</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>RNCA</t>
@@ -2129,7 +2135,9 @@
       <c r="K35" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" s="2" t="n">
+        <v>45888</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2178,7 +2186,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>a0R3g000008LwK0</t>
+          <t>a0R3g0000080gJl</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2204,13 +2212,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>15700000001</t>
+          <t>#KAIKU_SW</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="n">
-        <v>1</v>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>RNCA</t>
@@ -2224,7 +2230,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>a0R3g0000095FZo</t>
+          <t>a0RKf00000JPBkj</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2234,15 +2240,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>44294</v>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>12213_KAI01_2</t>
@@ -2254,7 +2262,9 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>RNCA</t>
@@ -2264,13 +2274,13 @@
         <v>37010</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>44343</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>a0R3g0000080gJl</t>
+          <t>a0R3g0000080gJq</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2296,7 +2306,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
+          <t>15700000016</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -2314,7 +2324,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>a0R3g0000080gIw</t>
+          <t>a0R3g0000095FZo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2340,7 +2350,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
+          <t>15700000016</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2353,12 +2363,14 @@
       <c r="K40" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" s="2" t="n">
+        <v>44343</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>a0R6g00000H26hv</t>
+          <t>a0R6g00000H2Eia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2368,12 +2380,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2384,10 +2396,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>60801000001SK</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>45348</v>
+      </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
@@ -2400,13 +2414,13 @@
         <v>41089</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>45322</v>
+        <v>45348</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>a0R6g00000H2EiY</t>
+          <t>a0R6g00000H2EiZ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2432,7 +2446,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
+          <t>60000000100SK</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
@@ -2456,7 +2470,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>a0R6g00000H2Eia</t>
+          <t>a0R6g00000H2EiY</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2482,7 +2496,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
+          <t>60502000000SK</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
@@ -2506,7 +2520,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>a0R6g00000H2EiZ</t>
+          <t>a0R6g00000H26Xh</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2516,12 +2530,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2532,12 +2546,10 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>60000000100SK</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>45348</v>
-      </c>
+          <t>1570000020S</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>1</v>
       </c>
@@ -2550,13 +2562,13 @@
         <v>41089</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>45348</v>
+        <v>45322</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>a0R6g00000H26Xh</t>
+          <t>a0R6g00000H26hv</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2582,7 +2594,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1570000020S</t>
+          <t>#KAIKU</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2652,7 +2664,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>a0R6g00000H0XVZ</t>
+          <t>a0R6g00000H0XVe</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2678,10 +2690,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>60801000001SK</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>45278</v>
+      </c>
       <c r="I47" t="n">
         <v>1</v>
       </c>
@@ -2693,12 +2707,14 @@
       <c r="K47" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" s="2" t="n">
+        <v>45386</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>a0R6g00000HgAfp</t>
+          <t>a0R6g00000H2rSP</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2717,7 +2733,7 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>45278</v>
+        <v>45274</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2726,7 +2742,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>15700000014</t>
+          <t>60000000100SK</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2742,13 +2758,13 @@
         <v>37010</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>45594</v>
+        <v>45386</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>a0R6g00000H2rSP</t>
+          <t>a0R6g00000H0XVU</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2758,28 +2774,28 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>12722_PLZ01_2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>60502000000SK</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
         <v>45278</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>12722_PLZ01_2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>60000000100SK</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>1</v>
       </c>
@@ -2798,7 +2814,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>a0R6g00000HgAfq</t>
+          <t>a0R6g00000H0XVZ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2808,17 +2824,15 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>45278</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>12722_PLZ01_2</t>
@@ -2826,7 +2840,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>15700000016</t>
+          <t>#KAIKU</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2841,9 +2855,7 @@
       <c r="K50" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L50" s="2" t="n">
-        <v>45594</v>
-      </c>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2867,7 +2879,7 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>45278</v>
+        <v>45274</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2898,7 +2910,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>a0R6g00000H0XVe</t>
+          <t>a0R6g00000H0XVa</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2924,12 +2936,10 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>45278</v>
-      </c>
+          <t>#KAIKU_SW</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>1</v>
       </c>
@@ -2941,14 +2951,12 @@
       <c r="K52" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L52" s="2" t="n">
-        <v>45386</v>
-      </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>a0R6g00000H0XVa</t>
+          <t>a0R6g00000HgAfq</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2958,15 +2966,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>45274</v>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>12722_PLZ01_2</t>
@@ -2974,7 +2984,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
+          <t>15700000016</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -2989,12 +2999,14 @@
       <c r="K53" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" s="2" t="n">
+        <v>45594</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>a0R6g00000H0XVU</t>
+          <t>a0R6g00000HgAfp</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3004,15 +3016,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>45274</v>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>12722_PLZ01_2</t>
@@ -3020,12 +3034,10 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>45278</v>
-      </c>
+          <t>15700000014</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>1</v>
       </c>
@@ -3038,13 +3050,13 @@
         <v>37010</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>45386</v>
+        <v>45594</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>a0R6g00000EWFz4</t>
+          <t>a0R6g00000EWG0A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3070,7 +3082,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>60000000100SK</t>
+          <t>60801000001SK</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
@@ -3094,7 +3106,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>a0R6g00000H2wNg</t>
+          <t>a0R6g00000EWFz4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3104,28 +3116,28 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>13606_KAI01_2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>60000000100SK</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
         <v>45216</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>13606_KAI01_2</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>15700000014</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>1</v>
       </c>
@@ -3138,13 +3150,13 @@
         <v>37675</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>45399</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>a0R6g00000H2wNh</t>
+          <t>a0R6g00000EWG05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3154,28 +3166,28 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>13606_KAI01_2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>60502000000SK</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n">
         <v>45216</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>13606_KAI01_2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>15700000016</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>1</v>
       </c>
@@ -3188,7 +3200,7 @@
         <v>37675</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>45399</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="58">
@@ -3242,7 +3254,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>a0R6g00000EWG05</t>
+          <t>a0R6g00000EWFz9</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3268,12 +3280,10 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>45216</v>
-      </c>
+          <t>#KAIKU</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>1</v>
       </c>
@@ -3285,14 +3295,12 @@
       <c r="K59" s="2" t="n">
         <v>37675</v>
       </c>
-      <c r="L59" s="2" t="n">
-        <v>45461</v>
-      </c>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>a0R6g00000EWFzA</t>
+          <t>a0R6g00000H2wNi</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3302,15 +3310,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>45216</v>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>13606_KAI01_2</t>
@@ -3318,7 +3328,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
+          <t>15700000027</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3333,12 +3343,14 @@
       <c r="K60" s="2" t="n">
         <v>37675</v>
       </c>
-      <c r="L60" t="inlineStr"/>
+      <c r="L60" s="2" t="n">
+        <v>45399</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>a0R6g00000H2wNi</t>
+          <t>a0R6g00000EWFzA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3348,17 +3360,15 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>45216</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>13606_KAI01_2</t>
@@ -3366,7 +3376,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>15700000027</t>
+          <t>#KAIKU_SW</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -3381,14 +3391,12 @@
       <c r="K61" s="2" t="n">
         <v>37675</v>
       </c>
-      <c r="L61" s="2" t="n">
-        <v>45399</v>
-      </c>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>a0R6g00000EWG0A</t>
+          <t>a0R6g00000H2wNh</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3398,15 +3406,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>45216</v>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>13606_KAI01_2</t>
@@ -3414,12 +3424,10 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>45216</v>
-      </c>
+          <t>15700000016</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>1</v>
       </c>
@@ -3432,13 +3440,13 @@
         <v>37675</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>45461</v>
+        <v>45399</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>a0R6g00000EWFz9</t>
+          <t>a0R6g00000H2wNg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3448,15 +3456,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>45216</v>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>13606_KAI01_2</t>
@@ -3464,7 +3474,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
+          <t>15700000014</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -3479,12 +3489,14 @@
       <c r="K63" s="2" t="n">
         <v>37675</v>
       </c>
-      <c r="L63" t="inlineStr"/>
+      <c r="L63" s="2" t="n">
+        <v>45399</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>a0R6g00000HfMUW</t>
+          <t>a0R6g00000H2hgO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3494,28 +3506,28 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>13727_PLZ01_2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>60801000001SK</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
         <v>45308</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>13727_PLZ01_2</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>15700000027</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>1</v>
       </c>
@@ -3528,13 +3540,13 @@
         <v>37010</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>45503</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>a0RKf00000Ew1nx</t>
+          <t>a0RKf00000Ew1o8</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3562,7 +3574,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>15700000016</t>
+          <t>60000000100SK</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -3584,7 +3596,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>a0R6g00000H2hgJ</t>
+          <t>a0R6g00000H2hgE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3610,10 +3622,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>60502000000SK</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>45308</v>
+      </c>
       <c r="I66" t="n">
         <v>1</v>
       </c>
@@ -3625,12 +3639,14 @@
       <c r="K66" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" s="2" t="n">
+        <v>45378</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>a0R6g00000H2hgO</t>
+          <t>a0R6g00000H2hgJ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3656,12 +3672,10 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>45308</v>
-      </c>
+          <t>#KAIKU</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
         <v>1</v>
       </c>
@@ -3673,14 +3687,12 @@
       <c r="K67" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L67" s="2" t="n">
-        <v>45378</v>
-      </c>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>a0R6g00000H2hgE</t>
+          <t>a0R6g00000HfMUW</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3690,15 +3702,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>45308</v>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>13727_PLZ01_2</t>
@@ -3706,12 +3720,10 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>45308</v>
-      </c>
+          <t>15700000027</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
         <v>1</v>
       </c>
@@ -3724,7 +3736,7 @@
         <v>37010</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>45378</v>
+        <v>45503</v>
       </c>
     </row>
     <row r="69">
@@ -3776,7 +3788,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>a0RKf00000Ew1o8</t>
+          <t>a0RKf00000Ew1nx</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3804,7 +3816,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>60000000100SK</t>
+          <t>15700000016</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -3876,7 +3888,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>a0R6g00000H36Dw</t>
+          <t>a0R6g00000H36EZ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3902,10 +3914,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>60801000001SK</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>45418</v>
+      </c>
       <c r="I72" t="n">
         <v>1</v>
       </c>
@@ -3917,7 +3931,9 @@
       <c r="K72" s="2" t="n">
         <v>38072</v>
       </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" s="2" t="n">
+        <v>45467</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3972,7 +3988,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>a0R6g00000H36EZ</t>
+          <t>a0R6g00000H36Et</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3998,7 +4014,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
+          <t>60502000000SK</t>
         </is>
       </c>
       <c r="H74" s="2" t="n">
@@ -4070,7 +4086,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>a0R6g00000H36Et</t>
+          <t>a0R6g00000H36Dw</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4096,12 +4112,10 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>45418</v>
-      </c>
+          <t>#KAIKU</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
         <v>1</v>
       </c>
@@ -4113,9 +4127,7 @@
       <c r="K76" s="2" t="n">
         <v>38072</v>
       </c>
-      <c r="L76" s="2" t="n">
-        <v>45467</v>
-      </c>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4166,7 +4178,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>a0RKf00000KfgM2</t>
+          <t>a0RKf00000KfgM4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4185,7 +4197,7 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>46112</v>
+        <v>45979</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4194,7 +4206,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
+          <t>60801000001SK</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -4216,7 +4228,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>a0RKf00000KfgM4</t>
+          <t>a0RKf00000KfgM3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4235,7 +4247,7 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>46112</v>
+        <v>45979</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4244,7 +4256,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
+          <t>60000000100SK</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -4266,7 +4278,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>a0RKf00000Kff68</t>
+          <t>a0RKf00000KfgM2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4276,15 +4288,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>45979</v>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>14535_PLZ01_2</t>
@@ -4292,7 +4306,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
+          <t>60502000000SK</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -4307,12 +4321,14 @@
       <c r="K80" s="2" t="n">
         <v>37592</v>
       </c>
-      <c r="L80" t="inlineStr"/>
+      <c r="L80" s="2" t="n">
+        <v>45979</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>a0RKf00000Kff5A</t>
+          <t>a0RQQ00000J4Vjp</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4338,10 +4354,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>1570000020S</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>46112</v>
+      </c>
       <c r="I81" t="n">
         <v>1</v>
       </c>
@@ -4353,12 +4371,14 @@
       <c r="K81" s="2" t="n">
         <v>37592</v>
       </c>
-      <c r="L81" t="inlineStr"/>
+      <c r="L81" s="2" t="n">
+        <v>46112</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>a0RKf00000KfgM3</t>
+          <t>a0RKf00000Kff5A</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4368,17 +4388,15 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>46112</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>14535_PLZ01_2</t>
@@ -4386,7 +4404,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>60000000100SK</t>
+          <t>#KAIKU</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -4401,14 +4419,12 @@
       <c r="K82" s="2" t="n">
         <v>37592</v>
       </c>
-      <c r="L82" s="2" t="n">
-        <v>45979</v>
-      </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>a0RQQ00000J4Vjp</t>
+          <t>a0RKf00000Kff68</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4434,12 +4450,10 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1570000020S</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>46112</v>
-      </c>
+          <t>#KAIKU_SW</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
         <v>1</v>
       </c>
@@ -4451,9 +4465,7 @@
       <c r="K83" s="2" t="n">
         <v>37592</v>
       </c>
-      <c r="L83" s="2" t="n">
-        <v>46112</v>
-      </c>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4508,7 +4520,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>a0RKf00000EvyJI</t>
+          <t>a0RKf00000EvyJY</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4534,7 +4546,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>15700000014</t>
+          <t>60801000001SK</t>
         </is>
       </c>
       <c r="H85" s="2" t="n">
@@ -4558,7 +4570,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>a0RKf00000EvyJW</t>
+          <t>a0RKf00000EvyJZ</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4586,7 +4598,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>60000000100SK</t>
+          <t>60801000001SK</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -4608,7 +4620,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>a0RKf00000JQ6qu</t>
+          <t>a0RKf00000EvyJV</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4634,10 +4646,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>60000000100SK</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>45595</v>
+      </c>
       <c r="I87" t="n">
         <v>1</v>
       </c>
@@ -4649,12 +4663,14 @@
       <c r="K87" s="2" t="n">
         <v>39287</v>
       </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" s="2" t="n">
+        <v>45762</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>a0RKf00000EvyJV</t>
+          <t>a0RKf00000EvyJW</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4664,15 +4680,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>45595</v>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>15004_PLZ01_2</t>
@@ -4683,9 +4701,7 @@
           <t>60000000100SK</t>
         </is>
       </c>
-      <c r="H88" s="2" t="n">
-        <v>45595</v>
-      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
         <v>1</v>
       </c>
@@ -4704,7 +4720,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>a0RKf00000EvyJP</t>
+          <t>a0RKf00000EvyJR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4730,7 +4746,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>15700000027</t>
+          <t>60502000000SK</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
@@ -4754,7 +4770,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>a0RKf00000EvyJR</t>
+          <t>a0RKf00000EvyJT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4764,15 +4780,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>45595</v>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>15004_PLZ01_2</t>
@@ -4783,9 +4801,7 @@
           <t>60502000000SK</t>
         </is>
       </c>
-      <c r="H90" s="2" t="n">
-        <v>45595</v>
-      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
         <v>1</v>
       </c>
@@ -4804,7 +4820,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>a0RKf00000EvyJY</t>
+          <t>a0RKf00000JQ6qu</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4830,12 +4846,10 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>45595</v>
-      </c>
+          <t>#KAIKU</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
         <v>1</v>
       </c>
@@ -4847,14 +4861,12 @@
       <c r="K91" s="2" t="n">
         <v>39287</v>
       </c>
-      <c r="L91" s="2" t="n">
-        <v>45762</v>
-      </c>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>a0RKf00000EvyJL</t>
+          <t>a0RKf00000EvyJP</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4880,7 +4892,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>15700000016</t>
+          <t>15700000027</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
@@ -4950,7 +4962,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>a0RKf00000EvyJT</t>
+          <t>a0RKf00000EvyJL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4960,28 +4972,28 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>15004_PLZ01_2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>15700000016</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n">
         <v>45595</v>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>15004_PLZ01_2</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>60502000000SK</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
         <v>1</v>
       </c>
@@ -5000,7 +5012,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>a0RKf00000EvyJZ</t>
+          <t>a0RKf00000EvyJI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5010,28 +5022,28 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>15004_PLZ01_2</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>15700000014</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n">
         <v>45595</v>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>15004_PLZ01_2</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>60801000001SK</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
         <v>1</v>
       </c>
@@ -5050,7 +5062,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>a0R6g00000F09tO</t>
+          <t>a0RKf00000Ew2BZ</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5060,15 +5072,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>44904</v>
+      </c>
       <c r="F96" t="inlineStr">
         <is>
           <t>30000142_KAI01_2</t>
@@ -5076,12 +5090,10 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>44904</v>
-      </c>
+          <t>60801000001SK</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
         <v>1</v>
       </c>
@@ -5094,13 +5106,13 @@
         <v>40016</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>45014</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>a0RKf00000Ew2BZ</t>
+          <t>a0RKf00000Ew2BY</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5128,7 +5140,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
+          <t>60000000100SK</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -5150,7 +5162,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>a0R6g00000EUktB</t>
+          <t>a0RKf00000Ew2BX</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5160,15 +5172,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>44904</v>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>30000142_KAI01_2</t>
@@ -5176,12 +5190,10 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>15700000028</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>44904</v>
-      </c>
+          <t>60502000000SK</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
         <v>1</v>
       </c>
@@ -5194,13 +5206,13 @@
         <v>40016</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>45014</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>a0RKf00000Ew2BX</t>
+          <t>a0R3g000009YmLV</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5210,28 +5222,28 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>30000142_KAI01_2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1570000020S</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n">
         <v>44904</v>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>30000142_KAI01_2</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>60502000000SK</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
         <v>1</v>
       </c>
@@ -5244,13 +5256,13 @@
         <v>40016</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>45763</v>
+        <v>44679</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>a0R6g00000EUkt7</t>
+          <t>a0R6g00000F09tO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5276,7 +5288,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>15700000014</t>
+          <t>#KAIKU</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
@@ -5300,7 +5312,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>a0R6g00000EUktA</t>
+          <t>a0R6g00000EUktB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5326,7 +5338,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>15700000017</t>
+          <t>15700000028</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
@@ -5350,7 +5362,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>a0RKf00000Ew2BY</t>
+          <t>a0R6g00000F09tT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5360,28 +5372,28 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>30000142_KAI01_2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>#KAIKU_SW</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n">
         <v>44904</v>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>30000142_KAI01_2</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>60000000100SK</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="n">
         <v>1</v>
       </c>
@@ -5394,13 +5406,13 @@
         <v>40016</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>45763</v>
+        <v>45014</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>a0R3g000009YmLV</t>
+          <t>a0R6g00000EUkt6</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5426,7 +5438,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1570000020S</t>
+          <t>15700000013</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
@@ -5444,13 +5456,13 @@
         <v>40016</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>44679</v>
+        <v>45014</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>a0R6g00000EUkt8</t>
+          <t>a0R6g00000EUktA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5476,7 +5488,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>15700000015</t>
+          <t>15700000017</t>
         </is>
       </c>
       <c r="H104" s="2" t="n">
@@ -5500,7 +5512,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>a0R6g00000EUkt6</t>
+          <t>a0R6g00000EUkt9</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5526,7 +5538,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>15700000013</t>
+          <t>15700000016</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
@@ -5550,7 +5562,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>a0R6g00000F09tT</t>
+          <t>a0R6g00000EUkt7</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5576,7 +5588,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
+          <t>15700000014</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
@@ -5600,7 +5612,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>a0R6g00000EUkt9</t>
+          <t>a0R6g00000EUkt8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5626,7 +5638,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>15700000016</t>
+          <t>15700000015</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
@@ -5650,7 +5662,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>a0R6g00000EWCoU</t>
+          <t>a0R6g00000H0XVo</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5660,12 +5672,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -5676,10 +5688,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>60801000001SK</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>45280</v>
+      </c>
       <c r="I108" t="n">
         <v>1</v>
       </c>
@@ -5692,7 +5706,7 @@
         <v>40851</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>45209</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="109">
@@ -5746,7 +5760,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>a0R6g00000H2pkj</t>
+          <t>a0R6g00000H0XVj</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5756,12 +5770,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -5772,10 +5786,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1570000020S</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>60502000000SK</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>45280</v>
+      </c>
       <c r="I110" t="n">
         <v>1</v>
       </c>
@@ -5794,7 +5810,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>a0R6g00000EWCoZ</t>
+          <t>a0R6g00000H2pkj</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5820,7 +5836,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
+          <t>1570000020S</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -5836,13 +5852,13 @@
         <v>40851</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>45209</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>a0R6g00000H0XVj</t>
+          <t>a0R6g00000EWCoU</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5852,12 +5868,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -5868,12 +5884,10 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>45280</v>
-      </c>
+          <t>#KAIKU</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
         <v>1</v>
       </c>
@@ -5886,13 +5900,13 @@
         <v>40851</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>45384</v>
+        <v>45209</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>a0R6g00000H0XVo</t>
+          <t>a0R6g00000EWCoZ</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5902,12 +5916,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -5918,12 +5932,10 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>45280</v>
-      </c>
+          <t>#KAIKU_SW</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
         <v>1</v>
       </c>
@@ -5936,13 +5948,13 @@
         <v>40851</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>45384</v>
+        <v>45209</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>a0RQQ00000HMFpq</t>
+          <t>a0RQQ00000HMFpr</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5961,7 +5973,7 @@
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>45413</v>
+        <v>45400</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5970,7 +5982,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>60000000100SK</t>
+          <t>60801000001SK</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -5992,7 +6004,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>a0R6g00000H2wm7</t>
+          <t>a0RQQ00000HMFpq</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6011,7 +6023,7 @@
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>45413</v>
+        <v>45400</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -6020,7 +6032,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>15700000014</t>
+          <t>60000000100SK</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
@@ -6036,13 +6048,13 @@
         <v>37010</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>45400</v>
+        <v>46056</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>a0RQQ00000HMFpr</t>
+          <t>a0RQQ00000HMFpp</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6061,7 +6073,7 @@
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>45413</v>
+        <v>45400</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -6070,7 +6082,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
+          <t>60502000000SK</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -6092,7 +6104,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>a0R6g00000H2zRL</t>
+          <t>a0R6g00000H2zRG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6118,7 +6130,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
+          <t>#KAIKU</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -6140,7 +6152,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>a0R6g00000H2zRG</t>
+          <t>a0RQQ00000HMjPl</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6150,15 +6162,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>45400</v>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
           <t>30000211_PLZ01_2</t>
@@ -6166,7 +6180,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
+          <t>15700000027</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -6182,13 +6196,13 @@
         <v>37010</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>45400</v>
+        <v>46056</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>a0RQQ00000HMFpp</t>
+          <t>a0R6g00000H2wm9</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6198,17 +6212,15 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>45413</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>30000211_PLZ01_2</t>
@@ -6216,7 +6228,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
+          <t>15700000027</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -6232,13 +6244,13 @@
         <v>37010</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>46056</v>
+        <v>45400</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>a0R6g00000H2wm9</t>
+          <t>a0R6g00000H2zRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6264,7 +6276,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>15700000027</t>
+          <t>#KAIKU_SW</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -6286,7 +6298,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>a0RQQ00000HMjPl</t>
+          <t>a0R6g00000H2wm8</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6296,28 +6308,28 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>30000211_PLZ01_2</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>15700000016</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n">
         <v>45413</v>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>30000211_PLZ01_2</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>15700000027</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
         <v>1</v>
       </c>
@@ -6330,13 +6342,13 @@
         <v>37010</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>46056</v>
+        <v>45400</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>a0R6g00000H2wm8</t>
+          <t>a0R6g00000H2wm7</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6346,15 +6358,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>45400</v>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
           <t>30000211_PLZ01_2</t>
@@ -6362,12 +6376,10 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>15700000016</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>45413</v>
-      </c>
+          <t>15700000014</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
         <v>1</v>
       </c>
@@ -6386,7 +6398,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>a0R6g00000Hgcva</t>
+          <t>a0R6g00000HgYe2</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6396,28 +6408,28 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>30002237_PLZ01_2</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>60801000001SK</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>30002237_PLZ01_2</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>15700000014</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
         <v>1</v>
       </c>
@@ -6436,7 +6448,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>a0R6g00000HgYe7</t>
+          <t>a0R6g00000HgYeR</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6462,10 +6474,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>60502000000SK</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>45657</v>
+      </c>
       <c r="I124" t="n">
         <v>1</v>
       </c>
@@ -6477,12 +6491,14 @@
       <c r="K124" s="2" t="n">
         <v>41968</v>
       </c>
-      <c r="L124" t="inlineStr"/>
+      <c r="L124" s="2" t="n">
+        <v>45678</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>a0R6g00000Hgcvb</t>
+          <t>a0R6g00000HgYe7</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6492,17 +6508,15 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>45657</v>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>30002237_PLZ01_2</t>
@@ -6510,7 +6524,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>15700000016</t>
+          <t>#KAIKU</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -6525,14 +6539,12 @@
       <c r="K125" s="2" t="n">
         <v>41968</v>
       </c>
-      <c r="L125" s="2" t="n">
-        <v>45678</v>
-      </c>
+      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>a0R6g00000HgYe2</t>
+          <t>a0R6g00000HgYe8</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6558,12 +6570,10 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>45657</v>
-      </c>
+          <t>#KAIKU_SW</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
         <v>1</v>
       </c>
@@ -6575,14 +6585,12 @@
       <c r="K126" s="2" t="n">
         <v>41968</v>
       </c>
-      <c r="L126" s="2" t="n">
-        <v>45678</v>
-      </c>
+      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>a0R6g00000HgYe8</t>
+          <t>a0R6g00000Hgcvb</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6592,15 +6600,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>45657</v>
+      </c>
       <c r="F127" t="inlineStr">
         <is>
           <t>30002237_PLZ01_2</t>
@@ -6608,7 +6618,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
+          <t>15700000016</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -6623,12 +6633,14 @@
       <c r="K127" s="2" t="n">
         <v>41968</v>
       </c>
-      <c r="L127" t="inlineStr"/>
+      <c r="L127" s="2" t="n">
+        <v>45678</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>a0R6g00000HgYeR</t>
+          <t>a0R6g00000Hgcva</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6638,15 +6650,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>45657</v>
+      </c>
       <c r="F128" t="inlineStr">
         <is>
           <t>30002237_PLZ01_2</t>
@@ -6654,12 +6668,10 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>45657</v>
-      </c>
+          <t>15700000014</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="n">
         <v>1</v>
       </c>
@@ -6678,7 +6690,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>a0R6g00000H2CgM</t>
+          <t>a0R6g00000H2Cgb</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6704,7 +6716,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
+          <t>60801000001SK</t>
         </is>
       </c>
       <c r="H129" s="2" t="n">
@@ -6728,7 +6740,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>a0R6g00000H2CgR</t>
+          <t>a0R6g00000HgdNt</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6738,15 +6750,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>45341</v>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>30004172_PLZ01_2</t>
@@ -6754,12 +6768,10 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>45341</v>
-      </c>
+          <t>60000000100SK</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="n">
         <v>1</v>
       </c>
@@ -6771,12 +6783,14 @@
       <c r="K130" s="2" t="n">
         <v>38011</v>
       </c>
-      <c r="L130" t="inlineStr"/>
+      <c r="L130" s="2" t="n">
+        <v>45679</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>a0R6g00000HgdNt</t>
+          <t>a0R6g00000H2CgM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6786,28 +6800,28 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>30004172_PLZ01_2</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>60502000000SK</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n">
         <v>45341</v>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>30004172_PLZ01_2</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>60000000100SK</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="n">
         <v>1</v>
       </c>
@@ -6826,7 +6840,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>a0R6g00000H2CgS</t>
+          <t>a0R6g00000H2CgR</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6852,7 +6866,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
+          <t>#KAIKU</t>
         </is>
       </c>
       <c r="H132" s="2" t="n">
@@ -6924,7 +6938,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>a0R6g00000H2Cgb</t>
+          <t>a0R6g00000H2CgS</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6950,7 +6964,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>60801000001SK</t>
+          <t>#KAIKU_SW</t>
         </is>
       </c>
       <c r="H134" s="2" t="n">
@@ -6967,14 +6981,12 @@
       <c r="K134" s="2" t="n">
         <v>38011</v>
       </c>
-      <c r="L134" s="2" t="n">
-        <v>45679</v>
-      </c>
+      <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>a0R6g00000H3EzH</t>
+          <t>a0R6g00000HfhWs</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6984,15 +6996,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>45442</v>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
           <t>30004672_RO01_2</t>
@@ -7000,7 +7014,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
+          <t>60801000001SK</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -7015,12 +7029,14 @@
       <c r="K135" s="2" t="n">
         <v>43305</v>
       </c>
-      <c r="L135" t="inlineStr"/>
+      <c r="L135" s="2" t="n">
+        <v>45532</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>a0R6g00000H3FRq</t>
+          <t>a0R6g00000H3EzC</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7046,12 +7062,10 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>60502000000SK</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>45443</v>
-      </c>
+          <t>60000000100SK</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="n">
         <v>1</v>
       </c>
@@ -7070,7 +7084,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>a0R6g00000HfhWs</t>
+          <t>a0R6g00000H3FRq</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7080,28 +7094,28 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="n">
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>30004672_RO01_2</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>60502000000SK</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="n">
         <v>45443</v>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>30004672_RO01_2</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>60801000001SK</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="n">
         <v>1</v>
       </c>
@@ -7120,7 +7134,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>a0R6g00000H3EzI</t>
+          <t>a0R6g00000HfAxx</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7146,7 +7160,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
+          <t>1570000020S</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -7161,12 +7175,14 @@
       <c r="K138" s="2" t="n">
         <v>43305</v>
       </c>
-      <c r="L138" t="inlineStr"/>
+      <c r="L138" s="2" t="n">
+        <v>45471</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>a0R6g00000HfAxx</t>
+          <t>a0R6g00000H3EzH</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7192,7 +7208,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>1570000020S</t>
+          <t>#KAIKU</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -7207,14 +7223,12 @@
       <c r="K139" s="2" t="n">
         <v>43305</v>
       </c>
-      <c r="L139" s="2" t="n">
-        <v>45471</v>
-      </c>
+      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>a0R6g00000H3EzC</t>
+          <t>a0R6g00000H3EzI</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7240,7 +7254,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>60000000100SK</t>
+          <t>#KAIKU_SW</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -7255,14 +7269,12 @@
       <c r="K140" s="2" t="n">
         <v>43305</v>
       </c>
-      <c r="L140" s="2" t="n">
-        <v>45532</v>
-      </c>
+      <c r="L140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>a0R6g00000HxKBR</t>
+          <t>a0RKf00000Kff71</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7272,12 +7284,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Installed</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -7288,7 +7300,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>15700000014</t>
+          <t>#KAIKU</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -7303,14 +7315,12 @@
       <c r="K141" s="2" t="n">
         <v>43209</v>
       </c>
-      <c r="L141" s="2" t="n">
-        <v>45735</v>
-      </c>
+      <c r="L141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>a0RKf00000Kff71</t>
+          <t>a0RKf00000Kff76</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7336,7 +7346,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>#KAIKU</t>
+          <t>#KAIKU_SW</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -7374,7 +7384,9 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
+      <c r="E143" s="3" t="n">
+        <v>45735</v>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
           <t>30006754_PLZ01_2</t>
@@ -7404,7 +7416,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>a0RKf00000Kff76</t>
+          <t>a0R6g00000HxKBR</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7414,15 +7426,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>45735</v>
+      </c>
       <c r="F144" t="inlineStr">
         <is>
           <t>30006754_PLZ01_2</t>
@@ -7430,7 +7444,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>#KAIKU_SW</t>
+          <t>15700000014</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -7445,7 +7459,9 @@
       <c r="K144" s="2" t="n">
         <v>43209</v>
       </c>
-      <c r="L144" t="inlineStr"/>
+      <c r="L144" s="2" t="n">
+        <v>45735</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Mass_update_KAIKU/mass_update_kaiku_sts_fix.xlsx
+++ b/Mass_update_KAIKU/mass_update_kaiku_sts_fix.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -60,12 +58,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -596,27 +593,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a0R3g000009enf7</t>
+          <t>a0R3g000009OPzK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Installed</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>44673</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>10451_KAI01_2</t>
@@ -639,24 +634,22 @@
       <c r="K4" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L4" s="2" t="n">
-        <v>44673</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a0R3g000009OPzK</t>
+          <t>a0R3g000009enf7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -687,7 +680,9 @@
       <c r="K5" s="2" t="n">
         <v>37010</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" s="2" t="n">
+        <v>44673</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Mass_update_KAIKU/mass_update_kaiku_sts_fix.xlsx
+++ b/Mass_update_KAIKU/mass_update_kaiku_sts_fix.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -58,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,64 +436,29 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>right sts</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>sts equals parent?</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>sts equals parent?</t>
+          <t>Date Installed</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Date Installed</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
           <t>Full Location Movex Id</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Product: Product Code</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Customer/Device Acceptance Date</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Account Region</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Date Shipped</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a0R3g000009enf1</t>
+          <t>a0R3g000009OPzK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -507,181 +468,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
         <is>
           <t>10451_KAI01_2</t>
         </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>15700000001</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>44673</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>a0R3g000009enf4</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10451_KAI01_2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>15700000007</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44673</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>a0R3g000009OPzK</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10451_KAI01_2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>15700000012</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>a0R3g000009enf7</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>10451_KAI01_2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>15700000012</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>RNCA</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>37010</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>44673</v>
       </c>
     </row>
   </sheetData>
